--- a/AAII_Financials/Quarterly/HD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>HD</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E7" s="2">
         <v>46145</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46054</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45963</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45872</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45781</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45690</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44409</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44318</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44136</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44045</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43954</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43863</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43772</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43681</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43590</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43499</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43401</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43219</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43128</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>47861000</v>
+      </c>
+      <c r="E8" s="3">
         <v>41765000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38198000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41352000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>45277000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>39856000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39704000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40217000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43175000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36418000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34786000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37710000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42916000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37257000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35831000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38872000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>43792000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38908000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35719000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36820000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41118000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37500000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32261000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>33536000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>38053000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28260000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>25782000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27223000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>30839000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>26381000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>26491000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>26302000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>30463000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>24947000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>23883000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>25026000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>28108000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>23887000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>22207000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>23154000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>32431000</v>
+      </c>
+      <c r="E9" s="3">
         <v>27984000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25732000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27537000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30152000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26397000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26670000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26792000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28759000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23985000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>23278000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24972000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28759000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24700000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>23905000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>25648000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>29309000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25763000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>23857000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24257000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27453000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24758000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21430000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>22080000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>25112000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>18635000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17046000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17836000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>20407000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17364000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17464000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17151000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>20098000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>16330000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>15790000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>16378000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>18647000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>15733000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>14654000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>15112000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15430000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13781000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12466000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13815000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15125000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13459000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13034000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13425000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14416000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12433000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11508000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12738000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14157000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12557000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11926000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13224000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14483000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13145000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11862000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12563000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13665000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12742000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10831000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11456000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12941000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9625000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8736000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9387000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>10432000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9017000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>9027000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9151000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10365000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8617000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8093000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8648000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>9461000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8154000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7553000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>8042000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1222,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1332,8 +1345,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1454,13 +1470,16 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-685000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1510,35 +1529,35 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>125000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>35000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>24000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>78000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>354000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>479000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>848000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1546,12 +1565,12 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>247000</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1567,8 +1586,8 @@
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
@@ -1576,130 +1595,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>852000</v>
+      </c>
+      <c r="E15" s="3">
         <v>841000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>845000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>826000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>806000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>796000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>814000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>795000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>738000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>687000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>686000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>683000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>653000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>651000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>625000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>608000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>616000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>606000</v>
       </c>
       <c r="U15" s="3">
         <v>606000</v>
       </c>
       <c r="V15" s="3">
+        <v>606000</v>
+      </c>
+      <c r="W15" s="3">
         <v>600000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>593000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>587000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>561000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>528000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>519000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>520000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>519000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>498000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>492000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>480000</v>
       </c>
       <c r="AG15" s="3">
         <v>480000</v>
       </c>
       <c r="AH15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AI15" s="3">
         <v>473000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>460000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>457000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>464000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>454000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>449000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>444000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>443000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>442000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1739,252 +1764,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41707000</v>
+      </c>
+      <c r="E17" s="3">
         <v>36784000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34349000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35999000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38722000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34723000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35209000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34799000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36641000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31339000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30643000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32304000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36327000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31706000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31079000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32724000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36582000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>32979000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30894000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31025000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34479000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31719000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>28178000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>28684000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31986000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>24984000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22379000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>23276000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>25943000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>22784000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>23113000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>22432000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>25562000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>21566000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20694000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>21346000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>23645000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>20538000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>19280000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>19834000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6154000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4981000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3849000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5353000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6555000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5133000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4495000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5418000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6534000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5079000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4143000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5406000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6589000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5551000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4752000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6148000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7210000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5929000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4825000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5795000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6639000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5781000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4083000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4852000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6067000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3276000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3403000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3947000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4896000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3597000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3378000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3870000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4901000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3381000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3189000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3680000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4463000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3349000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2927000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3320000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2027,8 +2059,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2071,574 +2104,589 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>43000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>18000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>10000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>11000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>17000</v>
       </c>
       <c r="AC20" s="3">
         <v>17000</v>
       </c>
       <c r="AD20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>22000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>19000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>15000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>25000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>22000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>23000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>22000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>16000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>13000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>11000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7006000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5822000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4694000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6179000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7361000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5929000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5309000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6213000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7272000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5766000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4829000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6089000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7242000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6202000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5554000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6898000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7958000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6659000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5577000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6524000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7355000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6490000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4759000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5494000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6691000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3900000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4015000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4563000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5475000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4159000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3931000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4436000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5457000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3935000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3741000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4220000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4989000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3867000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3437000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3826000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>583000</v>
+      </c>
+      <c r="E22" s="3">
         <v>611000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>594000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>628000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>575000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>615000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>638000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>625000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>573000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>485000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>513000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>487000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>469000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>474000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>451000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>413000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>381000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>372000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>341000</v>
       </c>
       <c r="V22" s="3">
         <v>341000</v>
       </c>
       <c r="W22" s="3">
+        <v>341000</v>
+      </c>
+      <c r="X22" s="3">
         <v>326000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>339000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>337000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>340000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>346000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>324000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>309000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>302000</v>
       </c>
       <c r="AE22" s="3">
         <v>302000</v>
       </c>
       <c r="AF22" s="3">
+        <v>302000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>288000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>269000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>249000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>272000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>261000</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>269000</v>
       </c>
       <c r="AL22" s="3">
         <v>269000</v>
       </c>
       <c r="AM22" s="3">
+        <v>269000</v>
+      </c>
+      <c r="AN22" s="3">
         <v>265000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>254000</v>
-      </c>
-      <c r="AO22" s="3">
-        <v>246000</v>
       </c>
       <c r="AP22" s="3">
         <v>246000</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>246000</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6315000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4377000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3298000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4757000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6005000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4542000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3887000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4823000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6045000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4651000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3685000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4968000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6161000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5110000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4344000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5742000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6831000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5560000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4502000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5469000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6318000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5448000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3756000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4523000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5730000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2969000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3111000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3667000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4613000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3324000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3113000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3646000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4655000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3142000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2943000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3433000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4214000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3108000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2692000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>3084000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1549000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1088000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>727000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1156000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1454000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1109000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>890000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1175000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1484000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1051000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>884000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1158000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1502000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1237000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>982000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1403000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1658000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1329000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1150000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1340000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1511000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1303000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>899000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1091000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1398000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>724000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>630000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>898000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1134000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>811000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>739000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>894000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1149000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>738000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>764000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1268000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1542000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1094000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>948000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1115000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2759,252 +2807,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3289000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2571000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3601000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4551000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3433000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2997000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3648000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4561000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3600000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2801000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3810000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4659000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3362000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4339000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5173000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4231000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3352000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4129000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4807000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2857000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3432000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4332000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2769000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3479000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2513000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2374000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2752000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2179000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2672000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2014000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3289000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2571000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3601000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4551000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3433000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2997000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3648000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4561000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3600000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2801000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3810000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4659000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3362000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4339000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5173000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4231000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3352000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4129000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4807000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2857000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3432000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4332000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2769000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3479000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2513000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2374000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2752000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2179000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2672000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2014000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3125,8 +3182,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3217,24 +3277,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>115000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-400000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3247,8 +3307,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3369,8 +3432,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3491,8 +3557,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3535,208 +3604,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-43000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-18000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-17000</v>
       </c>
       <c r="AC32" s="3">
         <v>-17000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-23000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-10000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3289000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2571000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3601000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4551000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3433000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2997000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3648000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4561000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3600000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2801000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3810000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4659000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3362000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4339000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5173000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4231000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3352000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4129000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4807000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2857000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3432000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4332000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2769000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3479000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2513000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2344000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2867000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1779000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2672000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2014000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3857,257 +3932,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3289000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2571000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3601000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4551000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3433000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2997000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3648000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4561000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3600000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2801000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3810000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4659000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3362000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4339000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5173000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4231000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3352000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4129000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4807000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2857000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3432000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4332000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2769000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3479000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2513000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2344000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2867000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1779000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2672000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2014000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E38" s="2">
         <v>46145</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46054</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45963</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45872</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45781</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45690</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44409</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44318</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44136</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44045</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43954</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43863</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43772</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43681</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43590</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43499</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43401</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43219</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43128</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4150,8 +4234,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4194,130 +4279,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2085000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1601000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1389000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1684000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2804000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1369000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1659000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1531000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1613000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4264000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3760000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2058000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2814000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1260000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2757000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2462000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1259000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2844000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2343000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5067000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4566000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6648000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7895000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>14652000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>14139000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>8696000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2133000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2193000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2547000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1882000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1778000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1764000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3490000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3599000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3595000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3549000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4830000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3565000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2538000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3589000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4438,496 +4527,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6963000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6624000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5597000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6765000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5878000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5886000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4903000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5782000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5503000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4105000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3328000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3932000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3836000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4213000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3317000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3732000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3725000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3936000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3426000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3533000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3322000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3624000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2992000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2666000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2562000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2610000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2106000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2231000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2274000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2317000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1936000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2171000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2164000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2296000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1952000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2166000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2187000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2164000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2029000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1995000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>26847000</v>
+      </c>
+      <c r="E44" s="3">
         <v>27280000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25817000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26203000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24843000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>25763000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23451000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23897000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23060000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22416000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>20976000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22805000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23265000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>25371000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>24886000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>25719000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>26088000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>25297000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>22068000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>20582000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>18909000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>19178000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16627000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>16155000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>13498000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>14989000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>14531000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>15711000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>14741000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15495000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>13925000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>14754000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>14044000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>14432000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>12748000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>13419000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>12868000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>13609000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>12549000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>13241000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1825000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1667000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1588000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1463000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1866000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1511000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1670000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1739000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2097000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1837000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1711000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1887000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1915000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1579000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1511000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1768000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1869000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1790000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1218000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1284000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1465000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1222000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>963000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1162000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>982000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1040000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1039000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>859000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>890000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1120000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1104000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>887000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>638000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>548000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>626000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>558000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>608000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>523000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37720000</v>
+      </c>
+      <c r="E46" s="3">
         <v>37172000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34391000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36115000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35391000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>34529000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31683000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32949000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32273000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32622000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29775000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30682000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31830000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32423000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32471000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33681000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32941000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>33867000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>29055000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>30466000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>28262000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>30672000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>28477000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34505000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>31361000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27277000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19810000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21174000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>20699000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>20553000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18529000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19809000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>20802000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>21214000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>18933000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>19682000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>20511000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>19896000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>17724000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>19348000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4970,8 +5074,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5048,252 +5152,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37447000</v>
+      </c>
+      <c r="E48" s="3">
         <v>37205000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37225000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36724000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35558000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35479000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35294000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35094000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35253000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33910000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34038000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32806000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33018000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32605000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32572000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31763000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31379000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31146000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31167000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30838000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>30710000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30537000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>30667000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>29281000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28823000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28331000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>28365000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28110000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>28176000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>27899000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22375000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>22054000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>21909000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>21928000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>22075000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>21960000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>22035000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>21789000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>21914000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>21840000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33381000</v>
+      </c>
+      <c r="E49" s="3">
         <v>32723000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32673000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32683000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28389000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28456000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28458000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28540000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28628000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8464000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12061000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7937000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7664000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7447000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7444000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7434000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7451000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7450000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7449000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7445000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7454000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7137000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7126000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2236000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2233000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2220000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2254000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2253000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2254000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2250000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2252000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2258000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2251000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2281000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2275000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2217000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2235000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2095000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2093000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2095000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5414,8 +5527,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5536,130 +5652,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>836000</v>
+      </c>
+      <c r="E52" s="3">
         <v>804000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>514000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>752000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>711000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>693000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>415000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>681000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>692000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4234000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>343000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4152000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3875000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3911000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3958000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3988000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4054000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4104000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4205000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4282000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4343000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4221000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4311000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>897000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>932000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>909000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>807000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>772000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>881000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>813000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>847000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1079000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1270000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1227000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1246000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1164000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1178000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1164000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1235000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1219000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5780,130 +5902,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>109384000</v>
+      </c>
+      <c r="E54" s="3">
         <v>107904000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>105095000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106274000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100049000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>99157000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96119000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97264000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>96846000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>79230000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76530000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>75577000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76387000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76386000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>76445000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>76866000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>75825000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>76567000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>71876000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>73031000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70769000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>72567000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70581000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66919000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>63349000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>58737000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>51236000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52309000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52010000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51515000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>44003000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>45200000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>46232000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>46650000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>44529000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>45023000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>45959000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>44944000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>42966000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>44502000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5946,8 +6074,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5990,740 +6119,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13585000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14373000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11491000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13237000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13086000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14696000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11938000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13506000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13206000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12563000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10037000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11478000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12104000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12630000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11443000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12402000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14348000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15367000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13462000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13375000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12817000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14494000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11606000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12899000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11691000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10056000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7787000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9240000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9494000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10311000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7755000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9054000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9407000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9726000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>7244000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8570000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8541000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9138000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7000000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>8054000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10461000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10165000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10849000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11088000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7736000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6234000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6172000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5782000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5108000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1844000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2418000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2388000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2363000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2304000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1231000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1224000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1757000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2463000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3482000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2436000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2428000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1164000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1416000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2491000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2476000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4200000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2813000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2513000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1315000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1456000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2395000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2452000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2203000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1549000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2761000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1323000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>545000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>544000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1252000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>543000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2981000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3533000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2689000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2589000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2642000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3608000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3442000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2689000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2794000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3478000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2790000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3088000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3098000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4173000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10436000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10654000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11729000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12557000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11749000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11092000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11421000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12100000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10144000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10005000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10032000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9092000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7775000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7812000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7989000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7906000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6566000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6690000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>6816000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6858000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6189000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>6109000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>6737000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>6756000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5881000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>5834000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34988000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35580000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32424000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34367000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30846000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31589000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28661000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29092000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28123000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24359000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22015000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23572000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24227000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25446000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>23110000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24280000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27834000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30387000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28693000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26903000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26666000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>27758000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23166000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>25395000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>24199000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23348000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>18375000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19565000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18798000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>19673000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16716000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18196000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>18426000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18133000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16194000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16002000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>15823000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>16438000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>14133000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>14431000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52727000</v>
+      </c>
+      <c r="E61" s="3">
         <v>53566000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55060000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54894000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54184000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>55718000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>56913000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58350000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>60300000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50162000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50683000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>46867000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47130000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>47124000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>41962000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>41740000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39271000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>39158000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>36604000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>36712000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>33746000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>34697000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35822000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32831000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32370000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>31622000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28670000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>26597000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27064000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>26804000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>26807000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>23332000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>23295000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>24244000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>24267000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>24266000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>24422000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>22393000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>22349000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>22338000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2202000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1986000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1953000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2014000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1863000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1901000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1943000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1953000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1929000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1943000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1925000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2955000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2739000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2500000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9811000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9548000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8483000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8731000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8275000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8381000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8288000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8364000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8294000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7158000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7194000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7257000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7307000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7229000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7308000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7181000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2358000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2352000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2502000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2586000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2614000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2212000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2160000</v>
-      </c>
-      <c r="AN62" s="3">
-        <v>2151000</v>
       </c>
       <c r="AO62" s="3">
         <v>2151000</v>
       </c>
       <c r="AP62" s="3">
+        <v>2151000</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>2111000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6844,8 +6992,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6966,8 +7117,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7088,130 +7242,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92767000</v>
+      </c>
+      <c r="E66" s="3">
         <v>94030000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92282000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>94158000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>89384000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91202000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89479000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91478000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>92426000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77410000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75486000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74147000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75052000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>76024000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>74883000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75568000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>75588000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>78276000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>73572000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>71996000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68700000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>70819000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>67282000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>65384000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63763000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>62227000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54352000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>53391000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53170000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53658000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>45881000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>43880000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44223000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44963000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>43075000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>42480000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>42405000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>40982000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>38633000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>38880000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7254,8 +7414,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7376,8 +7537,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7498,8 +7662,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7620,8 +7787,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7742,130 +7912,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>97949000</v>
+      </c>
+      <c r="E72" s="3">
         <v>95506000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>94537000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>94255000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>92943000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>90680000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>89533000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>88771000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>87357000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>85027000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>83656000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>82934000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>81213000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78651000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>76896000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>75467000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>73074000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69849000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>67580000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>65951000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>63560000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>60504000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>58134000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>56892000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>55074000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>52354000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>51729000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>50729000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>49446000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>47459000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>46423000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>45235000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>43543000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>41221000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>39935000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>39193000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>38073000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>36461000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>35519000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>34612000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7986,8 +8162,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8108,8 +8287,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8230,130 +8412,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16617000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13874000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12813000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12116000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10665000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7955000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6640000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5786000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4420000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1820000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1044000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1430000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1335000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>362000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1562000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1298000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>237000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-1709000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1696000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1035000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2069000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1748000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3299000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1535000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-414000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-3490000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-3116000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-1160000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-2143000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1878000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1320000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2009000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1687000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1454000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2543000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3554000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3962000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4333000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5622000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8474,257 +8662,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E80" s="2">
         <v>46145</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46054</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45963</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45872</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45781</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45690</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44409</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44318</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44136</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44045</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43954</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43863</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43772</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43681</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43590</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43499</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43401</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43219</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43128</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4766000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3289000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2571000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3601000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4551000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3433000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2997000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3648000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4561000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3600000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2801000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3810000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4659000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3873000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3362000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4339000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5173000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4231000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3352000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4129000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4807000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2857000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3432000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4332000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2245000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2481000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2769000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3479000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2513000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2344000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2867000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3506000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2404000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1779000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2672000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2014000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1744000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8767,130 +8964,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>865000</v>
+      </c>
+      <c r="E83" s="3">
         <v>855000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>864000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>857000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>830000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>785000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>782000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>779000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>707000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>793000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>759000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>743000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>746000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>727000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>759000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>743000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>746000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>727000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>734000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>714000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>711000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>703000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>666000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>631000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>615000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>607000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>595000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>594000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>560000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>547000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>549000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>541000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>530000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>532000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>529000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>518000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>510000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>505000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>499000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>496000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9011,8 +9212,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9133,8 +9337,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9255,8 +9462,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9377,8 +9587,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9499,130 +9712,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5390000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6032000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3347000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4010000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4643000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4325000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4671000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4233000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5409000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5497000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4733000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4234000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6591000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5614000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4594000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2839000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3393000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3789000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3185000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3439000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3637000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6310000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1424000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2586000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9092000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5737000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3059000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2121000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3830000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4713000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3002000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2129000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3926000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3981000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2290000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1879000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3298000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>4564000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1864000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1042000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9665,130 +9884,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-880000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-844000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1058000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-898000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-917000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-806000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1101000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-818000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-719000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-847000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-858000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-671000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-792000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-905000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-903000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-769000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-743000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-704000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-829000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-695000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-518000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-524000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-960000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-471000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-446000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-586000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-787000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-645000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-681000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-731000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-620000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-535000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-556000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-543000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-508000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-388000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-458000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-476000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-448000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9909,8 +10132,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10031,130 +10257,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1902000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1109000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1215000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5873000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-961000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-931000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-814000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18268000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-830000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1581000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1246000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-999000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-903000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-895000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-784000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-760000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-701000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-837000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-674000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-930000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-528000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8719000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-431000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-442000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-578000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-773000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-631000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-561000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-688000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-723000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-618000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-527000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-548000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-652000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-485000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-646000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-445000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-468000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-441000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10197,130 +10429,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2323000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2320000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>2289000</v>
       </c>
       <c r="F96" s="3">
         <v>2289000</v>
       </c>
       <c r="G96" s="3">
+        <v>2289000</v>
+      </c>
+      <c r="H96" s="3">
         <v>2288000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2286000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2235000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2234000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2231000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2229000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2079000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2089000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2097000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2118000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1933000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1946000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1948000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1962000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1721000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1738000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1751000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1775000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-1614000</v>
       </c>
       <c r="Z96" s="3">
         <v>-1614000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-1614000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1612000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1611000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1481000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1486000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1492000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1499000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1156000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1175000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1184000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1189000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1038000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1044000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1069000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-837000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-849000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10441,8 +10677,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10563,8 +10802,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10685,370 +10927,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2988000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4713000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2480000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>746000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2224000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3756000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3331000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3476000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>10259000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4146000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1520000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3657000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4078000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6188000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3446000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-749000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4219000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2579000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5011000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2275000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4764000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7070000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>442000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1628000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3247000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1450000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2320000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1990000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2713000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3775000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2240000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3366000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3414000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3400000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1617000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2604000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1568000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-3081000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2446000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1003000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E101" s="3">
         <v>72000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-93000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-25000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-51000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>70000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-87000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>40000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>42000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-103000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>42000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-103000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-61000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>11000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-25000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>41000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>96000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>40000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>17000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>129000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-94000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-29000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>25000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-71000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>181000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E102" s="3">
         <v>212000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-295000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1120000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1435000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-290000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>128000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-82000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2651000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>504000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1702000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-756000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1554000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>295000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1203000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1585000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>501000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2724000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>501000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2082000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1247000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6757000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>513000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5443000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6563000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-354000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>665000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>104000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1726000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-109000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>46000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1281000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1265000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1027000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1051000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-429000</v>
       </c>
     </row>
